--- a/CC_GrabAndGo_Week12_Kitchen_v1.xlsx
+++ b/CC_GrabAndGo_Week12_Kitchen_v1.xlsx
@@ -780,71 +780,71 @@
     <row r="6" ht="15" customHeight="1" s="34">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>Chicken Breast (cooked)</t>
-        </is>
-      </c>
-      <c r="B6" s="39" t="inlineStr"/>
-      <c r="C6" s="39" t="inlineStr"/>
+          <t>Carrot Chips</t>
+        </is>
+      </c>
+      <c r="B6" s="39" t="n"/>
+      <c r="C6" s="39" t="n"/>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>Protein</t>
+          <t>Produce</t>
         </is>
       </c>
       <c r="E6" s="39" t="n"/>
       <c r="F6" s="39" t="inlineStr">
         <is>
-          <t>Chicken Caesar Wraps, Bowls</t>
+          <t>Pickled Carrot Jars, Snack Cups</t>
         </is>
       </c>
     </row>
     <row r="7" ht="21.75" customHeight="1" s="34">
       <c r="A7" s="40" t="inlineStr">
         <is>
-          <t>Black Beans (canned)</t>
-        </is>
-      </c>
-      <c r="B7" s="40" t="inlineStr"/>
-      <c r="C7" s="40" t="inlineStr"/>
+          <t>Broccoli</t>
+        </is>
+      </c>
+      <c r="B7" s="40" t="n"/>
+      <c r="C7" s="40" t="n"/>
       <c r="D7" s="40" t="inlineStr">
         <is>
-          <t>Pantry</t>
+          <t>Produce</t>
         </is>
       </c>
       <c r="E7" s="40" t="n"/>
       <c r="F7" s="40" t="inlineStr">
         <is>
-          <t>Southwest Bowls, Empanadas</t>
+          <t>Broccoli Cheddar Bowl, Beef &amp; Broccoli Bowl</t>
         </is>
       </c>
     </row>
     <row r="8" ht="21.75" customHeight="1" s="34">
       <c r="A8" s="41" t="inlineStr">
         <is>
-          <t>Bell Peppers (mixed)</t>
-        </is>
-      </c>
-      <c r="B8" s="41" t="inlineStr"/>
-      <c r="C8" s="41" t="inlineStr"/>
+          <t>Dehydrated Hash Browns</t>
+        </is>
+      </c>
+      <c r="B8" s="41" t="n"/>
+      <c r="C8" s="41" t="n"/>
       <c r="D8" s="41" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Pantry</t>
         </is>
       </c>
       <c r="E8" s="41" t="n"/>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>Fajita Bowls, Wraps</t>
+          <t>Hash Brown Breakfast Bowls, Breakfast Tacos</t>
         </is>
       </c>
     </row>
     <row r="9" ht="21.75" customHeight="1" s="34">
       <c r="A9" s="40" t="inlineStr">
         <is>
-          <t>Cilantro</t>
-        </is>
-      </c>
-      <c r="B9" s="40" t="inlineStr"/>
-      <c r="C9" s="40" t="inlineStr"/>
+          <t>Sweet Potatoes</t>
+        </is>
+      </c>
+      <c r="B9" s="40" t="n"/>
+      <c r="C9" s="40" t="n"/>
       <c r="D9" s="40" t="inlineStr">
         <is>
           <t>Produce</t>
@@ -853,49 +853,25 @@
       <c r="E9" s="40" t="n"/>
       <c r="F9" s="40" t="inlineStr">
         <is>
-          <t>Bowls, Salsa, Garnish</t>
+          <t>Golden Hour Bowl, Harvest Bowl</t>
         </is>
       </c>
     </row>
     <row r="10" ht="21.75" customHeight="1" s="34">
-      <c r="A10" s="41" t="inlineStr">
-        <is>
-          <t>Greek Yogurt</t>
-        </is>
-      </c>
-      <c r="B10" s="41" t="inlineStr"/>
-      <c r="C10" s="41" t="inlineStr"/>
-      <c r="D10" s="41" t="inlineStr">
-        <is>
-          <t>Dairy</t>
-        </is>
-      </c>
+      <c r="A10" s="41" t="n"/>
+      <c r="B10" s="41" t="n"/>
+      <c r="C10" s="41" t="n"/>
+      <c r="D10" s="41" t="n"/>
       <c r="E10" s="41" t="n"/>
-      <c r="F10" s="41" t="inlineStr">
-        <is>
-          <t>Parfaits</t>
-        </is>
-      </c>
+      <c r="F10" s="41" t="n"/>
     </row>
     <row r="11" ht="21.75" customHeight="1" s="34">
-      <c r="A11" s="40" t="inlineStr">
-        <is>
-          <t>Apples</t>
-        </is>
-      </c>
-      <c r="B11" s="40" t="inlineStr"/>
-      <c r="C11" s="40" t="inlineStr"/>
-      <c r="D11" s="40" t="inlineStr">
-        <is>
-          <t>Produce</t>
-        </is>
-      </c>
+      <c r="A11" s="40" t="n"/>
+      <c r="B11" s="40" t="n"/>
+      <c r="C11" s="40" t="n"/>
+      <c r="D11" s="40" t="n"/>
       <c r="E11" s="40" t="n"/>
-      <c r="F11" s="40" t="inlineStr">
-        <is>
-          <t>Fruit Bowls, Snacking</t>
-        </is>
-      </c>
+      <c r="F11" s="40" t="n"/>
     </row>
     <row r="12" ht="21.75" customHeight="1" s="34">
       <c r="A12" s="41" t="inlineStr">
@@ -1042,7 +1018,7 @@
     <row r="20" ht="21.75" customHeight="1" s="34">
       <c r="A20" s="48" t="inlineStr">
         <is>
-          <t>Bean &amp; Cheese Breakfast Taco w/ 2 oz Salsa</t>
+          <t>Loaded Hash Brown Breakfast Bowl</t>
         </is>
       </c>
       <c r="B20" s="49" t="n">
@@ -1060,7 +1036,7 @@
       </c>
       <c r="F20" s="51" t="inlineStr">
         <is>
-          <t>Surplus black beans</t>
+          <t>Surplus hash browns</t>
         </is>
       </c>
     </row>
@@ -1083,14 +1059,10 @@
         <f>B21+C21+D21</f>
         <v/>
       </c>
-      <c r="F21" s="55" t="inlineStr">
-        <is>
-          <t>Surplus apples</t>
-        </is>
-      </c>
+      <c r="F21" s="55" t="n"/>
     </row>
     <row r="22" ht="21.75" customHeight="1" s="34">
-      <c r="A22" s="48" t="inlineStr"/>
+      <c r="A22" s="48" t="n"/>
       <c r="B22" s="49" t="n"/>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
@@ -1101,7 +1073,7 @@
       <c r="F22" s="48" t="n"/>
     </row>
     <row r="23" ht="21.75" customHeight="1" s="34">
-      <c r="A23" s="52" t="inlineStr"/>
+      <c r="A23" s="52" t="n"/>
       <c r="B23" s="53" t="n"/>
       <c r="C23" s="53" t="n"/>
       <c r="D23" s="53" t="n"/>
@@ -1150,7 +1122,7 @@
     <row r="26" ht="21.75" customHeight="1" s="34">
       <c r="A26" s="48" t="inlineStr">
         <is>
-          <t>Chicken Caesar Salad</t>
+          <t>Broccoli Crunch Salad</t>
         </is>
       </c>
       <c r="B26" s="49" t="n">
@@ -1168,37 +1140,23 @@
       </c>
       <c r="F26" s="51" t="inlineStr">
         <is>
-          <t>Surplus chicken</t>
+          <t>Surplus broccoli</t>
         </is>
       </c>
     </row>
     <row r="27" ht="21.75" customHeight="1" s="34">
-      <c r="A27" s="52" t="inlineStr">
-        <is>
-          <t>Southwest Black Bean Salad</t>
-        </is>
-      </c>
-      <c r="B27" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" s="53" t="n">
-        <v>0</v>
-      </c>
+      <c r="A27" s="52" t="n"/>
+      <c r="B27" s="53" t="n"/>
+      <c r="C27" s="53" t="n"/>
+      <c r="D27" s="53" t="n"/>
       <c r="E27" s="54">
         <f>B27+C27+D27</f>
         <v/>
       </c>
-      <c r="F27" s="52" t="inlineStr">
-        <is>
-          <t>Surplus black beans &amp; peppers</t>
-        </is>
-      </c>
+      <c r="F27" s="52" t="n"/>
     </row>
     <row r="28" ht="21.75" customHeight="1" s="34">
-      <c r="A28" s="48" t="inlineStr"/>
+      <c r="A28" s="48" t="n"/>
       <c r="B28" s="49" t="n"/>
       <c r="C28" s="49" t="n"/>
       <c r="D28" s="49" t="n"/>
@@ -1247,7 +1205,7 @@
     <row r="31" ht="21.75" customHeight="1" s="34">
       <c r="A31" s="48" t="inlineStr">
         <is>
-          <t>Chicken Caesar Wrap</t>
+          <t>Roasted Sweet Potato &amp; Black Bean Wrap</t>
         </is>
       </c>
       <c r="B31" s="49" t="n">
@@ -1265,37 +1223,23 @@
       </c>
       <c r="F31" s="51" t="inlineStr">
         <is>
-          <t>Surplus chicken</t>
+          <t>Surplus sweet potatoes</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21.75" customHeight="1" s="34">
-      <c r="A32" s="52" t="inlineStr">
-        <is>
-          <t>Southwest Chicken Wrap w/ 2 oz Salsa</t>
-        </is>
-      </c>
-      <c r="B32" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C32" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" s="53" t="n">
-        <v>0</v>
-      </c>
+      <c r="A32" s="52" t="n"/>
+      <c r="B32" s="53" t="n"/>
+      <c r="C32" s="53" t="n"/>
+      <c r="D32" s="53" t="n"/>
       <c r="E32" s="54">
         <f>B32+C32+D32</f>
         <v/>
       </c>
-      <c r="F32" s="52" t="inlineStr">
-        <is>
-          <t>Surplus chicken &amp; peppers</t>
-        </is>
-      </c>
+      <c r="F32" s="52" t="n"/>
     </row>
     <row r="33" ht="21.75" customHeight="1" s="34">
-      <c r="A33" s="48" t="inlineStr"/>
+      <c r="A33" s="48" t="n"/>
       <c r="B33" s="49" t="n"/>
       <c r="C33" s="49" t="n"/>
       <c r="D33" s="49" t="n"/>
@@ -1344,7 +1288,7 @@
     <row r="36" ht="21.75" customHeight="1" s="34">
       <c r="A36" s="48" t="inlineStr">
         <is>
-          <t>Chicken Fajita Bowl (Rice)</t>
+          <t>Beef &amp; Broccoli Stir-Fry Bowl (Rice)</t>
         </is>
       </c>
       <c r="B36" s="49" t="n">
@@ -1362,14 +1306,14 @@
       </c>
       <c r="F36" s="51" t="inlineStr">
         <is>
-          <t>Surplus chicken &amp; peppers</t>
+          <t>Surplus broccoli</t>
         </is>
       </c>
     </row>
     <row r="37" ht="21.75" customHeight="1" s="34">
       <c r="A37" s="52" t="inlineStr">
         <is>
-          <t>Southwest Black Bean &amp; Rice Bowl</t>
+          <t>Broccoli Cheddar Mac Bowl</t>
         </is>
       </c>
       <c r="B37" s="53" t="n">
@@ -1387,18 +1331,18 @@
       </c>
       <c r="F37" s="55" t="inlineStr">
         <is>
-          <t>Surplus black beans &amp; peppers</t>
+          <t>Surplus broccoli</t>
         </is>
       </c>
     </row>
     <row r="38" ht="21.75" customHeight="1" s="34">
       <c r="A38" s="48" t="inlineStr">
         <is>
-          <t>Cilantro Lime Chicken Bowl (Rice)</t>
+          <t>Golden Hour Sweet Potato Bowl</t>
         </is>
       </c>
       <c r="B38" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" s="49" t="n">
         <v>4</v>
@@ -1412,23 +1356,37 @@
       </c>
       <c r="F38" s="51" t="inlineStr">
         <is>
-          <t>Surplus chicken &amp; cilantro</t>
+          <t>Surplus sweet potatoes</t>
         </is>
       </c>
     </row>
     <row r="39" ht="21.75" customHeight="1" s="34">
-      <c r="A39" s="52" t="inlineStr"/>
-      <c r="B39" s="53" t="n"/>
-      <c r="C39" s="53" t="n"/>
-      <c r="D39" s="53" t="n"/>
+      <c r="A39" s="52" t="inlineStr">
+        <is>
+          <t>Harvest Sweet Potato Bowl</t>
+        </is>
+      </c>
+      <c r="B39" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" s="53" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="54">
         <f>B39+C39+D39</f>
         <v/>
       </c>
-      <c r="F39" s="55" t="n"/>
+      <c r="F39" s="55" t="inlineStr">
+        <is>
+          <t>Surplus sweet potatoes</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="21.75" customHeight="1" s="34">
-      <c r="A40" s="48" t="inlineStr"/>
+      <c r="A40" s="48" t="n"/>
       <c r="B40" s="49" t="n"/>
       <c r="C40" s="49" t="n"/>
       <c r="D40" s="49" t="n"/>
@@ -1439,7 +1397,7 @@
       <c r="F40" s="48" t="n"/>
     </row>
     <row r="41" ht="21.75" customHeight="1" s="34">
-      <c r="A41" s="52" t="inlineStr"/>
+      <c r="A41" s="52" t="n"/>
       <c r="B41" s="53" t="n"/>
       <c r="C41" s="53" t="n"/>
       <c r="D41" s="53" t="n"/>
@@ -1513,10 +1471,10 @@
         </is>
       </c>
       <c r="B45" s="53" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C45" s="53" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D45" s="53" t="n">
         <v>0</v>
@@ -1525,21 +1483,39 @@
         <f>B45+C45+D45</f>
         <v/>
       </c>
-      <c r="F45" s="55" t="n"/>
+      <c r="F45" s="55" t="inlineStr">
+        <is>
+          <t>Surplus carrot chips</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="21.75" customHeight="1" s="34">
-      <c r="A46" s="48" t="inlineStr"/>
-      <c r="B46" s="49" t="n"/>
-      <c r="C46" s="49" t="n"/>
-      <c r="D46" s="49" t="n"/>
+      <c r="A46" s="48" t="inlineStr">
+        <is>
+          <t>Carrot Chip Snack Cup w/ Ranch</t>
+        </is>
+      </c>
+      <c r="B46" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="49" t="n">
+        <v>6</v>
+      </c>
       <c r="E46" s="50">
         <f>B46+C46+D46</f>
         <v/>
       </c>
-      <c r="F46" s="48" t="n"/>
+      <c r="F46" s="48" t="inlineStr">
+        <is>
+          <t>Surplus carrot chips</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="34">
-      <c r="A47" s="52" t="inlineStr"/>
+      <c r="A47" s="52" t="n"/>
       <c r="B47" s="53" t="n"/>
       <c r="C47" s="53" t="n"/>
       <c r="D47" s="53" t="n"/>
@@ -1588,7 +1564,7 @@
     <row r="50" ht="21.75" customHeight="1" s="34">
       <c r="A50" s="48" t="inlineStr">
         <is>
-          <t>Apple Cinnamon Granola Parfait</t>
+          <t>Sweet Potato Pie Parfait</t>
         </is>
       </c>
       <c r="B50" s="49" t="n">
@@ -1606,12 +1582,12 @@
       </c>
       <c r="F50" s="51" t="inlineStr">
         <is>
-          <t>Surplus apples &amp; yogurt</t>
+          <t>Surplus sweet potatoes</t>
         </is>
       </c>
     </row>
     <row r="51" ht="21.75" customHeight="1" s="34">
-      <c r="A51" s="52" t="inlineStr"/>
+      <c r="A51" s="52" t="n"/>
       <c r="B51" s="53" t="n"/>
       <c r="C51" s="53" t="n"/>
       <c r="D51" s="53" t="n"/>
@@ -1622,7 +1598,7 @@
       <c r="F51" s="52" t="n"/>
     </row>
     <row r="52" ht="21.75" customHeight="1" s="34">
-      <c r="A52" s="48" t="inlineStr"/>
+      <c r="A52" s="48" t="n"/>
       <c r="B52" s="49" t="n"/>
       <c r="C52" s="49" t="n"/>
       <c r="D52" s="49" t="n"/>

--- a/CC_GrabAndGo_Week12_Kitchen_v1.xlsx
+++ b/CC_GrabAndGo_Week12_Kitchen_v1.xlsx
@@ -793,7 +793,7 @@
       <c r="E6" s="39" t="n"/>
       <c r="F6" s="39" t="inlineStr">
         <is>
-          <t>Pickled Carrot Jars, Snack Cups</t>
+          <t>Pickled Carrot Jars</t>
         </is>
       </c>
     </row>
@@ -1311,29 +1311,12 @@
       </c>
     </row>
     <row r="37" ht="21.75" customHeight="1" s="34">
-      <c r="A37" s="52" t="inlineStr">
-        <is>
-          <t>Broccoli Cheddar Mac Bowl</t>
-        </is>
-      </c>
-      <c r="B37" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C37" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="D37" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="54">
-        <f>B37+C37+D37</f>
-        <v/>
-      </c>
-      <c r="F37" s="55" t="inlineStr">
-        <is>
-          <t>Surplus broccoli</t>
-        </is>
-      </c>
+      <c r="A37" s="52" t="n"/>
+      <c r="B37" s="53" t="n"/>
+      <c r="C37" s="53" t="n"/>
+      <c r="D37" s="53" t="n"/>
+      <c r="E37" s="54" t="n"/>
+      <c r="F37" s="55" t="n"/>
     </row>
     <row r="38" ht="21.75" customHeight="1" s="34">
       <c r="A38" s="48" t="inlineStr">
@@ -1490,29 +1473,12 @@
       </c>
     </row>
     <row r="46" ht="21.75" customHeight="1" s="34">
-      <c r="A46" s="48" t="inlineStr">
-        <is>
-          <t>Carrot Chip Snack Cup w/ Ranch</t>
-        </is>
-      </c>
-      <c r="B46" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="C46" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="D46" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="E46" s="50">
-        <f>B46+C46+D46</f>
-        <v/>
-      </c>
-      <c r="F46" s="48" t="inlineStr">
-        <is>
-          <t>Surplus carrot chips</t>
-        </is>
-      </c>
+      <c r="A46" s="48" t="n"/>
+      <c r="B46" s="49" t="n"/>
+      <c r="C46" s="49" t="n"/>
+      <c r="D46" s="49" t="n"/>
+      <c r="E46" s="50" t="n"/>
+      <c r="F46" s="48" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="34">
       <c r="A47" s="52" t="n"/>
@@ -1562,29 +1528,12 @@
       <c r="F49" s="44" t="n"/>
     </row>
     <row r="50" ht="21.75" customHeight="1" s="34">
-      <c r="A50" s="48" t="inlineStr">
-        <is>
-          <t>Sweet Potato Pie Parfait</t>
-        </is>
-      </c>
-      <c r="B50" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="C50" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="D50" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="50">
-        <f>B50+C50+D50</f>
-        <v/>
-      </c>
-      <c r="F50" s="51" t="inlineStr">
-        <is>
-          <t>Surplus sweet potatoes</t>
-        </is>
-      </c>
+      <c r="A50" s="48" t="n"/>
+      <c r="B50" s="49" t="n"/>
+      <c r="C50" s="49" t="n"/>
+      <c r="D50" s="49" t="n"/>
+      <c r="E50" s="50" t="n"/>
+      <c r="F50" s="51" t="n"/>
     </row>
     <row r="51" ht="21.75" customHeight="1" s="34">
       <c r="A51" s="52" t="n"/>
@@ -2282,8 +2231,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>

--- a/CC_GrabAndGo_Week12_Kitchen_v1.xlsx
+++ b/CC_GrabAndGo_Week12_Kitchen_v1.xlsx
@@ -1018,7 +1018,7 @@
     <row r="20" ht="21.75" customHeight="1" s="34">
       <c r="A20" s="48" t="inlineStr">
         <is>
-          <t>Loaded Hash Brown Breakfast Bowl</t>
+          <t>Potato Breakfast Taco w/ 2 oz Salsa</t>
         </is>
       </c>
       <c r="B20" s="49" t="n">
@@ -1036,36 +1036,50 @@
       </c>
       <c r="F20" s="51" t="inlineStr">
         <is>
-          <t>Surplus hash browns</t>
+          <t>Weekly staple</t>
         </is>
       </c>
     </row>
     <row r="21" ht="21.75" customHeight="1" s="34">
       <c r="A21" s="52" t="inlineStr">
         <is>
-          <t>Fruit Bowl</t>
+          <t>Loaded Hash Brown Breakfast Bowl</t>
         </is>
       </c>
       <c r="B21" s="53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C21" s="53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D21" s="53" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E21" s="54">
         <f>B21+C21+D21</f>
         <v/>
       </c>
-      <c r="F21" s="55" t="n"/>
+      <c r="F21" s="55" t="inlineStr">
+        <is>
+          <t>Surplus hash browns</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="21.75" customHeight="1" s="34">
-      <c r="A22" s="48" t="n"/>
-      <c r="B22" s="49" t="n"/>
-      <c r="C22" s="49" t="n"/>
-      <c r="D22" s="49" t="n"/>
+      <c r="A22" s="48" t="inlineStr">
+        <is>
+          <t>Fruit Bowl</t>
+        </is>
+      </c>
+      <c r="B22" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="50">
         <f>B22+C22+D22</f>
         <v/>
@@ -2231,8 +2245,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
     <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A5:F5"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>

--- a/CC_GrabAndGo_Week12_Kitchen_v1.xlsx
+++ b/CC_GrabAndGo_Week12_Kitchen_v1.xlsx
@@ -853,7 +853,7 @@
       <c r="E9" s="40" t="n"/>
       <c r="F9" s="40" t="inlineStr">
         <is>
-          <t>Golden Hour Bowl, Harvest Bowl</t>
+          <t>Golden Hour Bowl, Harvest Bowl, Sweet Potato Wrap, Parfait</t>
         </is>
       </c>
     </row>
@@ -1159,10 +1159,20 @@
       </c>
     </row>
     <row r="27" ht="21.75" customHeight="1" s="34">
-      <c r="A27" s="52" t="n"/>
-      <c r="B27" s="53" t="n"/>
-      <c r="C27" s="53" t="n"/>
-      <c r="D27" s="53" t="n"/>
+      <c r="A27" s="52" t="inlineStr">
+        <is>
+          <t>Southwest Chicken Salad</t>
+        </is>
+      </c>
+      <c r="B27" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="53" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="54">
         <f>B27+C27+D27</f>
         <v/>
@@ -1170,10 +1180,20 @@
       <c r="F27" s="52" t="n"/>
     </row>
     <row r="28" ht="21.75" customHeight="1" s="34">
-      <c r="A28" s="48" t="n"/>
-      <c r="B28" s="49" t="n"/>
-      <c r="C28" s="49" t="n"/>
-      <c r="D28" s="49" t="n"/>
+      <c r="A28" s="48" t="inlineStr">
+        <is>
+          <t>Garden Side Salad w/ Ranch</t>
+        </is>
+      </c>
+      <c r="B28" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="50">
         <f>B28+C28+D28</f>
         <v/>
@@ -1242,10 +1262,20 @@
       </c>
     </row>
     <row r="32" ht="21.75" customHeight="1" s="34">
-      <c r="A32" s="52" t="n"/>
-      <c r="B32" s="53" t="n"/>
-      <c r="C32" s="53" t="n"/>
-      <c r="D32" s="53" t="n"/>
+      <c r="A32" s="52" t="inlineStr">
+        <is>
+          <t>Chicken Caesar Wrap</t>
+        </is>
+      </c>
+      <c r="B32" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="53" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="54">
         <f>B32+C32+D32</f>
         <v/>
@@ -1253,10 +1283,20 @@
       <c r="F32" s="52" t="n"/>
     </row>
     <row r="33" ht="21.75" customHeight="1" s="34">
-      <c r="A33" s="48" t="n"/>
-      <c r="B33" s="49" t="n"/>
-      <c r="C33" s="49" t="n"/>
-      <c r="D33" s="49" t="n"/>
+      <c r="A33" s="48" t="inlineStr">
+        <is>
+          <t>Turkey &amp; Swiss on Sourdough</t>
+        </is>
+      </c>
+      <c r="B33" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="50">
         <f>B33+C33+D33</f>
         <v/>
@@ -1360,7 +1400,7 @@
     <row r="39" ht="21.75" customHeight="1" s="34">
       <c r="A39" s="52" t="inlineStr">
         <is>
-          <t>Harvest Sweet Potato Bowl</t>
+          <t>Mac &amp; Cheese Bowl</t>
         </is>
       </c>
       <c r="B39" s="53" t="n">
@@ -1487,10 +1527,20 @@
       </c>
     </row>
     <row r="46" ht="21.75" customHeight="1" s="34">
-      <c r="A46" s="48" t="n"/>
-      <c r="B46" s="49" t="n"/>
-      <c r="C46" s="49" t="n"/>
-      <c r="D46" s="49" t="n"/>
+      <c r="A46" s="48" t="inlineStr">
+        <is>
+          <t>Chips &amp; Salsa Cup</t>
+        </is>
+      </c>
+      <c r="B46" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="49" t="n">
+        <v>6</v>
+      </c>
       <c r="E46" s="50" t="n"/>
       <c r="F46" s="48" t="n"/>
     </row>
@@ -1542,23 +1592,47 @@
       <c r="F49" s="44" t="n"/>
     </row>
     <row r="50" ht="21.75" customHeight="1" s="34">
-      <c r="A50" s="48" t="n"/>
-      <c r="B50" s="49" t="n"/>
-      <c r="C50" s="49" t="n"/>
-      <c r="D50" s="49" t="n"/>
+      <c r="A50" s="48" t="inlineStr">
+        <is>
+          <t>Blueberry Granola Parfait</t>
+        </is>
+      </c>
+      <c r="B50" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="E50" s="50" t="n"/>
       <c r="F50" s="51" t="n"/>
     </row>
     <row r="51" ht="21.75" customHeight="1" s="34">
-      <c r="A51" s="52" t="n"/>
-      <c r="B51" s="53" t="n"/>
-      <c r="C51" s="53" t="n"/>
-      <c r="D51" s="53" t="n"/>
+      <c r="A51" s="52" t="inlineStr">
+        <is>
+          <t>Sweet Potato Cinnamon Parfait</t>
+        </is>
+      </c>
+      <c r="B51" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" s="53" t="n">
+        <v>0</v>
+      </c>
       <c r="E51" s="54">
         <f>B51+C51+D51</f>
         <v/>
       </c>
-      <c r="F51" s="52" t="n"/>
+      <c r="F51" s="52" t="inlineStr">
+        <is>
+          <t>Surplus sweet potatoes</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="21.75" customHeight="1" s="34">
       <c r="A52" s="48" t="n"/>
@@ -2245,8 +2319,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>

--- a/CC_GrabAndGo_Week12_Kitchen_v1.xlsx
+++ b/CC_GrabAndGo_Week12_Kitchen_v1.xlsx
@@ -1710,7 +1710,7 @@
     <row r="58" ht="15" customHeight="1" s="34">
       <c r="A58" s="63" t="inlineStr">
         <is>
-          <t>Shelf life: Salads &amp; Wraps 3 days | Lunch Bowls 5 days | Parfaits 3 days.</t>
+          <t>Shelf life: Salads &amp; Wraps 3 days | Lunch Bowls 4 days | Parfaits 3 days.</t>
         </is>
       </c>
     </row>
@@ -2319,8 +2319,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
     <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A5:F5"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>

--- a/CC_GrabAndGo_Week12_Kitchen_v1.xlsx
+++ b/CC_GrabAndGo_Week12_Kitchen_v1.xlsx
@@ -1423,10 +1423,20 @@
       </c>
     </row>
     <row r="40" ht="21.75" customHeight="1" s="34">
-      <c r="A40" s="48" t="n"/>
-      <c r="B40" s="49" t="n"/>
-      <c r="C40" s="49" t="n"/>
-      <c r="D40" s="49" t="n"/>
+      <c r="A40" s="48" t="inlineStr">
+        <is>
+          <t>Spaghetti &amp; Meatballs w/ Tomato Basil Sauce</t>
+        </is>
+      </c>
+      <c r="B40" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="50">
         <f>B40+C40+D40</f>
         <v/>
@@ -2319,8 +2329,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>

--- a/CC_GrabAndGo_Week12_Kitchen_v1.xlsx
+++ b/CC_GrabAndGo_Week12_Kitchen_v1.xlsx
@@ -1503,7 +1503,7 @@
         <v>5</v>
       </c>
       <c r="D44" s="49" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E44" s="50">
         <f>B44+C44+D44</f>
@@ -2329,8 +2329,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
     <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A5:F5"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>
